--- a/downloads/korrigierte_referenz/FestivalCrew_2NF.xlsx
+++ b/downloads/korrigierte_referenz/FestivalCrew_2NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="Rc36d535bfd9e43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="2" r:id="Rd4e10578a6eb498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="3" r:id="Rb64d19817d1d411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="Re17f175eb1b44636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="2" r:id="R64d87e83118f428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="3" r:id="R3951b0ccd12e49ee"/>
   </x:sheets>
 </x:workbook>
 </file>
